--- a/Data/EC/NIT-9007252938.xlsx
+++ b/Data/EC/NIT-9007252938.xlsx
@@ -5,12 +5,12 @@
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Laura Wilches\Documents\2_ Macro Comfenalco Cartagena\Macro Aviso Incumplimiento y demás\Estados De Cuenta\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Operaciones\OneDrive - NIYARAKY COLOMBIA SAS OLD2\Escritorio\2- MACRO COMFENALCO CARTAGENA ACTUALIZACION\2- MACRO COMFENALCO CARTAGENA ACTUALIZACION\Estados De Cuenta\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{ECD3032B-4809-4A86-8D0D-BBEE7E01E72A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{4BE8EE2F-B0DE-4606-A20A-3CD592CB9507}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-98" yWindow="-98" windowWidth="21795" windowHeight="12975" xr2:uid="{AD68D7A8-1C3D-47C5-9B6B-BED1C7738D4A}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11040" xr2:uid="{1310709F-B9EB-43AD-98CA-A05CEBAA01EE}"/>
   </bookViews>
   <sheets>
     <sheet name="Hoja1" sheetId="1" r:id="rId1"/>
@@ -716,22 +716,22 @@
   <xdr:twoCellAnchor>
     <xdr:from>
       <xdr:col>1</xdr:col>
-      <xdr:colOff>633769</xdr:colOff>
+      <xdr:colOff>717113</xdr:colOff>
       <xdr:row>1</xdr:row>
-      <xdr:rowOff>55950</xdr:rowOff>
+      <xdr:rowOff>75000</xdr:rowOff>
     </xdr:from>
     <xdr:to>
       <xdr:col>2</xdr:col>
-      <xdr:colOff>437794</xdr:colOff>
+      <xdr:colOff>435413</xdr:colOff>
       <xdr:row>4</xdr:row>
-      <xdr:rowOff>125025</xdr:rowOff>
+      <xdr:rowOff>115500</xdr:rowOff>
     </xdr:to>
     <xdr:pic>
       <xdr:nvPicPr>
         <xdr:cNvPr id="3" name="Imagen 2">
           <a:extLst>
             <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{06B054E8-0082-7E46-7514-0AAD99E49D90}"/>
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{7EFB45C5-75C5-8B9C-4702-B3CCF548BAE2}"/>
             </a:ext>
           </a:extLst>
         </xdr:cNvPr>
@@ -740,7 +740,7 @@
         </xdr:cNvPicPr>
       </xdr:nvPicPr>
       <xdr:blipFill>
-        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId1">
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId1" cstate="print">
           <a:extLst>
             <a:ext uri="{28A0092B-C50C-407E-A947-70E740481C1C}">
               <a14:useLocalDpi xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" val="0"/>
@@ -753,7 +753,7 @@
       </xdr:blipFill>
       <xdr:spPr>
         <a:xfrm>
-          <a:off x="890944" y="236925"/>
+          <a:off x="964763" y="265500"/>
           <a:ext cx="975600" cy="612000"/>
         </a:xfrm>
         <a:prstGeom prst="rect">
@@ -1082,23 +1082,23 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{2A6B0D12-26D5-498E-B515-5840601496D8}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{2695ADEC-0F70-477C-AED1-BB73AA82A3F8}">
   <dimension ref="B2:J123"/>
-  <sheetFormatPr baseColWidth="10" defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
+  <sheetFormatPr baseColWidth="10" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="3.59765625" customWidth="1"/>
-    <col min="2" max="2" width="18.9296875" style="2" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="17" style="2" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="34.265625" style="2" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="13.73046875" style="2" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="10.1328125" style="2" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="14.59765625" style="2" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="19.59765625" bestFit="1" customWidth="1"/>
-    <col min="9" max="9" width="18.265625" bestFit="1" customWidth="1"/>
-    <col min="10" max="10" width="15" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="3.7109375" customWidth="1"/>
+    <col min="2" max="2" width="19.7109375" style="2" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="17.7109375" style="2" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="35.42578125" style="2" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="14.28515625" style="2" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="11" style="2" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="15.28515625" style="2" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="20.42578125" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="19.140625" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="15.42578125" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="2" spans="2:10" x14ac:dyDescent="0.45">
+    <row r="2" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B2" s="3"/>
       <c r="C2" s="28"/>
       <c r="D2" s="29" t="s">
@@ -1111,7 +1111,7 @@
       <c r="I2" s="29"/>
       <c r="J2" s="29"/>
     </row>
-    <row r="3" spans="2:10" x14ac:dyDescent="0.45">
+    <row r="3" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B3" s="3"/>
       <c r="C3" s="28"/>
       <c r="D3" s="30"/>
@@ -1122,7 +1122,7 @@
       <c r="I3" s="30"/>
       <c r="J3" s="30"/>
     </row>
-    <row r="4" spans="2:10" x14ac:dyDescent="0.45">
+    <row r="4" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B4" s="3"/>
       <c r="C4" s="28"/>
       <c r="D4" s="30"/>
@@ -1133,7 +1133,7 @@
       <c r="I4" s="30"/>
       <c r="J4" s="30"/>
     </row>
-    <row r="5" spans="2:10" x14ac:dyDescent="0.45">
+    <row r="5" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B5" s="3"/>
       <c r="C5" s="28"/>
       <c r="D5" s="31"/>
@@ -1144,8 +1144,8 @@
       <c r="I5" s="31"/>
       <c r="J5" s="31"/>
     </row>
-    <row r="6" spans="2:10" ht="9" customHeight="1" x14ac:dyDescent="0.45"/>
-    <row r="7" spans="2:10" x14ac:dyDescent="0.45">
+    <row r="6" spans="2:10" ht="9" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="7" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B7" s="4" t="s">
         <v>94</v>
       </c>
@@ -1160,8 +1160,8 @@
       <c r="I7" s="6"/>
       <c r="J7" s="6"/>
     </row>
-    <row r="8" spans="2:10" ht="7.5" customHeight="1" x14ac:dyDescent="0.45"/>
-    <row r="9" spans="2:10" x14ac:dyDescent="0.45">
+    <row r="8" spans="2:10" ht="7.5" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="9" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B9" s="4" t="s">
         <v>6</v>
       </c>
@@ -1176,8 +1176,8 @@
       <c r="I9" s="6"/>
       <c r="J9" s="6"/>
     </row>
-    <row r="10" spans="2:10" ht="6.75" customHeight="1" x14ac:dyDescent="0.45"/>
-    <row r="11" spans="2:10" x14ac:dyDescent="0.45">
+    <row r="10" spans="2:10" ht="6.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="11" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B11" s="4" t="s">
         <v>95</v>
       </c>
@@ -1192,8 +1192,8 @@
       <c r="I11" s="7"/>
       <c r="J11" s="7"/>
     </row>
-    <row r="12" spans="2:10" ht="4.5" customHeight="1" x14ac:dyDescent="0.45"/>
-    <row r="13" spans="2:10" x14ac:dyDescent="0.45">
+    <row r="12" spans="2:10" ht="4.5" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="13" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B13" s="9" t="s">
         <v>96</v>
       </c>
@@ -1212,7 +1212,7 @@
       <c r="I13" s="5"/>
       <c r="J13" s="5"/>
     </row>
-    <row r="15" spans="2:10" x14ac:dyDescent="0.45">
+    <row r="15" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B15" s="10" t="s">
         <v>0</v>
       </c>
@@ -1241,7 +1241,7 @@
         <v>100</v>
       </c>
     </row>
-    <row r="16" spans="2:10" x14ac:dyDescent="0.45">
+    <row r="16" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B16" s="15" t="s">
         <v>8</v>
       </c>
@@ -1264,7 +1264,7 @@
       <c r="I16" s="19"/>
       <c r="J16" s="20"/>
     </row>
-    <row r="17" spans="2:10" x14ac:dyDescent="0.45">
+    <row r="17" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B17" s="15" t="s">
         <v>8</v>
       </c>
@@ -1287,7 +1287,7 @@
       <c r="I17" s="19"/>
       <c r="J17" s="20"/>
     </row>
-    <row r="18" spans="2:10" x14ac:dyDescent="0.45">
+    <row r="18" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B18" s="15" t="s">
         <v>8</v>
       </c>
@@ -1310,7 +1310,7 @@
       <c r="I18" s="19"/>
       <c r="J18" s="20"/>
     </row>
-    <row r="19" spans="2:10" x14ac:dyDescent="0.45">
+    <row r="19" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B19" s="15" t="s">
         <v>8</v>
       </c>
@@ -1333,7 +1333,7 @@
       <c r="I19" s="19"/>
       <c r="J19" s="20"/>
     </row>
-    <row r="20" spans="2:10" x14ac:dyDescent="0.45">
+    <row r="20" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B20" s="15" t="s">
         <v>8</v>
       </c>
@@ -1356,7 +1356,7 @@
       <c r="I20" s="19"/>
       <c r="J20" s="20"/>
     </row>
-    <row r="21" spans="2:10" x14ac:dyDescent="0.45">
+    <row r="21" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B21" s="15" t="s">
         <v>8</v>
       </c>
@@ -1379,7 +1379,7 @@
       <c r="I21" s="19"/>
       <c r="J21" s="20"/>
     </row>
-    <row r="22" spans="2:10" x14ac:dyDescent="0.45">
+    <row r="22" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B22" s="15" t="s">
         <v>8</v>
       </c>
@@ -1402,7 +1402,7 @@
       <c r="I22" s="19"/>
       <c r="J22" s="20"/>
     </row>
-    <row r="23" spans="2:10" x14ac:dyDescent="0.45">
+    <row r="23" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B23" s="15" t="s">
         <v>8</v>
       </c>
@@ -1425,7 +1425,7 @@
       <c r="I23" s="19"/>
       <c r="J23" s="20"/>
     </row>
-    <row r="24" spans="2:10" x14ac:dyDescent="0.45">
+    <row r="24" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B24" s="15" t="s">
         <v>8</v>
       </c>
@@ -1448,7 +1448,7 @@
       <c r="I24" s="19"/>
       <c r="J24" s="20"/>
     </row>
-    <row r="25" spans="2:10" x14ac:dyDescent="0.45">
+    <row r="25" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B25" s="15" t="s">
         <v>8</v>
       </c>
@@ -1471,7 +1471,7 @@
       <c r="I25" s="19"/>
       <c r="J25" s="20"/>
     </row>
-    <row r="26" spans="2:10" x14ac:dyDescent="0.45">
+    <row r="26" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B26" s="15" t="s">
         <v>8</v>
       </c>
@@ -1494,7 +1494,7 @@
       <c r="I26" s="19"/>
       <c r="J26" s="20"/>
     </row>
-    <row r="27" spans="2:10" x14ac:dyDescent="0.45">
+    <row r="27" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B27" s="15" t="s">
         <v>8</v>
       </c>
@@ -1517,7 +1517,7 @@
       <c r="I27" s="19"/>
       <c r="J27" s="20"/>
     </row>
-    <row r="28" spans="2:10" x14ac:dyDescent="0.45">
+    <row r="28" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B28" s="15" t="s">
         <v>8</v>
       </c>
@@ -1540,7 +1540,7 @@
       <c r="I28" s="19"/>
       <c r="J28" s="20"/>
     </row>
-    <row r="29" spans="2:10" x14ac:dyDescent="0.45">
+    <row r="29" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B29" s="15" t="s">
         <v>8</v>
       </c>
@@ -1563,7 +1563,7 @@
       <c r="I29" s="19"/>
       <c r="J29" s="20"/>
     </row>
-    <row r="30" spans="2:10" x14ac:dyDescent="0.45">
+    <row r="30" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B30" s="15" t="s">
         <v>8</v>
       </c>
@@ -1586,7 +1586,7 @@
       <c r="I30" s="19"/>
       <c r="J30" s="20"/>
     </row>
-    <row r="31" spans="2:10" x14ac:dyDescent="0.45">
+    <row r="31" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B31" s="15" t="s">
         <v>8</v>
       </c>
@@ -1609,7 +1609,7 @@
       <c r="I31" s="19"/>
       <c r="J31" s="20"/>
     </row>
-    <row r="32" spans="2:10" x14ac:dyDescent="0.45">
+    <row r="32" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B32" s="15" t="s">
         <v>8</v>
       </c>
@@ -1632,7 +1632,7 @@
       <c r="I32" s="19"/>
       <c r="J32" s="20"/>
     </row>
-    <row r="33" spans="2:10" x14ac:dyDescent="0.45">
+    <row r="33" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B33" s="15" t="s">
         <v>8</v>
       </c>
@@ -1655,7 +1655,7 @@
       <c r="I33" s="19"/>
       <c r="J33" s="20"/>
     </row>
-    <row r="34" spans="2:10" x14ac:dyDescent="0.45">
+    <row r="34" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B34" s="15" t="s">
         <v>8</v>
       </c>
@@ -1678,7 +1678,7 @@
       <c r="I34" s="19"/>
       <c r="J34" s="20"/>
     </row>
-    <row r="35" spans="2:10" x14ac:dyDescent="0.45">
+    <row r="35" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B35" s="15" t="s">
         <v>8</v>
       </c>
@@ -1701,7 +1701,7 @@
       <c r="I35" s="19"/>
       <c r="J35" s="20"/>
     </row>
-    <row r="36" spans="2:10" x14ac:dyDescent="0.45">
+    <row r="36" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B36" s="15" t="s">
         <v>8</v>
       </c>
@@ -1724,7 +1724,7 @@
       <c r="I36" s="19"/>
       <c r="J36" s="20"/>
     </row>
-    <row r="37" spans="2:10" x14ac:dyDescent="0.45">
+    <row r="37" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B37" s="15" t="s">
         <v>8</v>
       </c>
@@ -1747,7 +1747,7 @@
       <c r="I37" s="19"/>
       <c r="J37" s="20"/>
     </row>
-    <row r="38" spans="2:10" x14ac:dyDescent="0.45">
+    <row r="38" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B38" s="15" t="s">
         <v>8</v>
       </c>
@@ -1770,7 +1770,7 @@
       <c r="I38" s="19"/>
       <c r="J38" s="20"/>
     </row>
-    <row r="39" spans="2:10" x14ac:dyDescent="0.45">
+    <row r="39" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B39" s="15" t="s">
         <v>8</v>
       </c>
@@ -1793,7 +1793,7 @@
       <c r="I39" s="19"/>
       <c r="J39" s="20"/>
     </row>
-    <row r="40" spans="2:10" x14ac:dyDescent="0.45">
+    <row r="40" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B40" s="15" t="s">
         <v>8</v>
       </c>
@@ -1816,7 +1816,7 @@
       <c r="I40" s="19"/>
       <c r="J40" s="20"/>
     </row>
-    <row r="41" spans="2:10" x14ac:dyDescent="0.45">
+    <row r="41" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B41" s="15" t="s">
         <v>8</v>
       </c>
@@ -1839,7 +1839,7 @@
       <c r="I41" s="19"/>
       <c r="J41" s="20"/>
     </row>
-    <row r="42" spans="2:10" x14ac:dyDescent="0.45">
+    <row r="42" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B42" s="15" t="s">
         <v>8</v>
       </c>
@@ -1862,7 +1862,7 @@
       <c r="I42" s="19"/>
       <c r="J42" s="20"/>
     </row>
-    <row r="43" spans="2:10" x14ac:dyDescent="0.45">
+    <row r="43" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B43" s="15" t="s">
         <v>8</v>
       </c>
@@ -1885,7 +1885,7 @@
       <c r="I43" s="19"/>
       <c r="J43" s="20"/>
     </row>
-    <row r="44" spans="2:10" x14ac:dyDescent="0.45">
+    <row r="44" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B44" s="15" t="s">
         <v>8</v>
       </c>
@@ -1908,7 +1908,7 @@
       <c r="I44" s="19"/>
       <c r="J44" s="20"/>
     </row>
-    <row r="45" spans="2:10" x14ac:dyDescent="0.45">
+    <row r="45" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B45" s="15" t="s">
         <v>8</v>
       </c>
@@ -1931,7 +1931,7 @@
       <c r="I45" s="19"/>
       <c r="J45" s="20"/>
     </row>
-    <row r="46" spans="2:10" x14ac:dyDescent="0.45">
+    <row r="46" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B46" s="15" t="s">
         <v>8</v>
       </c>
@@ -1954,7 +1954,7 @@
       <c r="I46" s="19"/>
       <c r="J46" s="20"/>
     </row>
-    <row r="47" spans="2:10" x14ac:dyDescent="0.45">
+    <row r="47" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B47" s="15" t="s">
         <v>8</v>
       </c>
@@ -1977,7 +1977,7 @@
       <c r="I47" s="19"/>
       <c r="J47" s="20"/>
     </row>
-    <row r="48" spans="2:10" x14ac:dyDescent="0.45">
+    <row r="48" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B48" s="15" t="s">
         <v>8</v>
       </c>
@@ -2000,7 +2000,7 @@
       <c r="I48" s="19"/>
       <c r="J48" s="20"/>
     </row>
-    <row r="49" spans="2:10" x14ac:dyDescent="0.45">
+    <row r="49" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B49" s="15" t="s">
         <v>8</v>
       </c>
@@ -2023,7 +2023,7 @@
       <c r="I49" s="19"/>
       <c r="J49" s="20"/>
     </row>
-    <row r="50" spans="2:10" x14ac:dyDescent="0.45">
+    <row r="50" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B50" s="15" t="s">
         <v>8</v>
       </c>
@@ -2046,7 +2046,7 @@
       <c r="I50" s="19"/>
       <c r="J50" s="20"/>
     </row>
-    <row r="51" spans="2:10" x14ac:dyDescent="0.45">
+    <row r="51" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B51" s="15" t="s">
         <v>8</v>
       </c>
@@ -2069,7 +2069,7 @@
       <c r="I51" s="19"/>
       <c r="J51" s="20"/>
     </row>
-    <row r="52" spans="2:10" x14ac:dyDescent="0.45">
+    <row r="52" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B52" s="15" t="s">
         <v>8</v>
       </c>
@@ -2092,7 +2092,7 @@
       <c r="I52" s="19"/>
       <c r="J52" s="20"/>
     </row>
-    <row r="53" spans="2:10" x14ac:dyDescent="0.45">
+    <row r="53" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B53" s="15" t="s">
         <v>8</v>
       </c>
@@ -2115,7 +2115,7 @@
       <c r="I53" s="19"/>
       <c r="J53" s="20"/>
     </row>
-    <row r="54" spans="2:10" x14ac:dyDescent="0.45">
+    <row r="54" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B54" s="15" t="s">
         <v>8</v>
       </c>
@@ -2138,7 +2138,7 @@
       <c r="I54" s="19"/>
       <c r="J54" s="20"/>
     </row>
-    <row r="55" spans="2:10" x14ac:dyDescent="0.45">
+    <row r="55" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B55" s="15" t="s">
         <v>8</v>
       </c>
@@ -2161,7 +2161,7 @@
       <c r="I55" s="19"/>
       <c r="J55" s="20"/>
     </row>
-    <row r="56" spans="2:10" x14ac:dyDescent="0.45">
+    <row r="56" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B56" s="15" t="s">
         <v>8</v>
       </c>
@@ -2184,7 +2184,7 @@
       <c r="I56" s="19"/>
       <c r="J56" s="20"/>
     </row>
-    <row r="57" spans="2:10" x14ac:dyDescent="0.45">
+    <row r="57" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B57" s="15" t="s">
         <v>8</v>
       </c>
@@ -2207,7 +2207,7 @@
       <c r="I57" s="19"/>
       <c r="J57" s="20"/>
     </row>
-    <row r="58" spans="2:10" x14ac:dyDescent="0.45">
+    <row r="58" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B58" s="15" t="s">
         <v>8</v>
       </c>
@@ -2230,7 +2230,7 @@
       <c r="I58" s="19"/>
       <c r="J58" s="20"/>
     </row>
-    <row r="59" spans="2:10" x14ac:dyDescent="0.45">
+    <row r="59" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B59" s="15" t="s">
         <v>8</v>
       </c>
@@ -2253,7 +2253,7 @@
       <c r="I59" s="19"/>
       <c r="J59" s="20"/>
     </row>
-    <row r="60" spans="2:10" x14ac:dyDescent="0.45">
+    <row r="60" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B60" s="15" t="s">
         <v>8</v>
       </c>
@@ -2276,7 +2276,7 @@
       <c r="I60" s="19"/>
       <c r="J60" s="20"/>
     </row>
-    <row r="61" spans="2:10" x14ac:dyDescent="0.45">
+    <row r="61" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B61" s="15" t="s">
         <v>8</v>
       </c>
@@ -2299,7 +2299,7 @@
       <c r="I61" s="19"/>
       <c r="J61" s="20"/>
     </row>
-    <row r="62" spans="2:10" x14ac:dyDescent="0.45">
+    <row r="62" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B62" s="15" t="s">
         <v>8</v>
       </c>
@@ -2322,7 +2322,7 @@
       <c r="I62" s="19"/>
       <c r="J62" s="20"/>
     </row>
-    <row r="63" spans="2:10" x14ac:dyDescent="0.45">
+    <row r="63" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B63" s="15" t="s">
         <v>8</v>
       </c>
@@ -2345,7 +2345,7 @@
       <c r="I63" s="19"/>
       <c r="J63" s="20"/>
     </row>
-    <row r="64" spans="2:10" x14ac:dyDescent="0.45">
+    <row r="64" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B64" s="15" t="s">
         <v>8</v>
       </c>
@@ -2368,7 +2368,7 @@
       <c r="I64" s="19"/>
       <c r="J64" s="20"/>
     </row>
-    <row r="65" spans="2:10" x14ac:dyDescent="0.45">
+    <row r="65" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B65" s="15" t="s">
         <v>8</v>
       </c>
@@ -2391,7 +2391,7 @@
       <c r="I65" s="19"/>
       <c r="J65" s="20"/>
     </row>
-    <row r="66" spans="2:10" x14ac:dyDescent="0.45">
+    <row r="66" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B66" s="15" t="s">
         <v>8</v>
       </c>
@@ -2414,7 +2414,7 @@
       <c r="I66" s="19"/>
       <c r="J66" s="20"/>
     </row>
-    <row r="67" spans="2:10" x14ac:dyDescent="0.45">
+    <row r="67" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B67" s="15" t="s">
         <v>8</v>
       </c>
@@ -2437,7 +2437,7 @@
       <c r="I67" s="19"/>
       <c r="J67" s="20"/>
     </row>
-    <row r="68" spans="2:10" x14ac:dyDescent="0.45">
+    <row r="68" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B68" s="15" t="s">
         <v>8</v>
       </c>
@@ -2460,7 +2460,7 @@
       <c r="I68" s="19"/>
       <c r="J68" s="20"/>
     </row>
-    <row r="69" spans="2:10" x14ac:dyDescent="0.45">
+    <row r="69" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B69" s="15" t="s">
         <v>8</v>
       </c>
@@ -2483,7 +2483,7 @@
       <c r="I69" s="19"/>
       <c r="J69" s="20"/>
     </row>
-    <row r="70" spans="2:10" x14ac:dyDescent="0.45">
+    <row r="70" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B70" s="15" t="s">
         <v>8</v>
       </c>
@@ -2506,7 +2506,7 @@
       <c r="I70" s="19"/>
       <c r="J70" s="20"/>
     </row>
-    <row r="71" spans="2:10" x14ac:dyDescent="0.45">
+    <row r="71" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B71" s="15" t="s">
         <v>8</v>
       </c>
@@ -2529,7 +2529,7 @@
       <c r="I71" s="19"/>
       <c r="J71" s="20"/>
     </row>
-    <row r="72" spans="2:10" x14ac:dyDescent="0.45">
+    <row r="72" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B72" s="15" t="s">
         <v>8</v>
       </c>
@@ -2552,7 +2552,7 @@
       <c r="I72" s="19"/>
       <c r="J72" s="20"/>
     </row>
-    <row r="73" spans="2:10" x14ac:dyDescent="0.45">
+    <row r="73" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B73" s="15" t="s">
         <v>8</v>
       </c>
@@ -2575,7 +2575,7 @@
       <c r="I73" s="19"/>
       <c r="J73" s="20"/>
     </row>
-    <row r="74" spans="2:10" x14ac:dyDescent="0.45">
+    <row r="74" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B74" s="15" t="s">
         <v>8</v>
       </c>
@@ -2598,7 +2598,7 @@
       <c r="I74" s="19"/>
       <c r="J74" s="20"/>
     </row>
-    <row r="75" spans="2:10" x14ac:dyDescent="0.45">
+    <row r="75" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B75" s="15" t="s">
         <v>8</v>
       </c>
@@ -2621,7 +2621,7 @@
       <c r="I75" s="19"/>
       <c r="J75" s="20"/>
     </row>
-    <row r="76" spans="2:10" x14ac:dyDescent="0.45">
+    <row r="76" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B76" s="15" t="s">
         <v>8</v>
       </c>
@@ -2644,7 +2644,7 @@
       <c r="I76" s="19"/>
       <c r="J76" s="20"/>
     </row>
-    <row r="77" spans="2:10" x14ac:dyDescent="0.45">
+    <row r="77" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B77" s="15" t="s">
         <v>8</v>
       </c>
@@ -2667,7 +2667,7 @@
       <c r="I77" s="19"/>
       <c r="J77" s="20"/>
     </row>
-    <row r="78" spans="2:10" x14ac:dyDescent="0.45">
+    <row r="78" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B78" s="15" t="s">
         <v>8</v>
       </c>
@@ -2690,7 +2690,7 @@
       <c r="I78" s="19"/>
       <c r="J78" s="20"/>
     </row>
-    <row r="79" spans="2:10" x14ac:dyDescent="0.45">
+    <row r="79" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B79" s="15" t="s">
         <v>8</v>
       </c>
@@ -2713,7 +2713,7 @@
       <c r="I79" s="19"/>
       <c r="J79" s="20"/>
     </row>
-    <row r="80" spans="2:10" x14ac:dyDescent="0.45">
+    <row r="80" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B80" s="15" t="s">
         <v>8</v>
       </c>
@@ -2736,7 +2736,7 @@
       <c r="I80" s="19"/>
       <c r="J80" s="20"/>
     </row>
-    <row r="81" spans="2:10" x14ac:dyDescent="0.45">
+    <row r="81" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B81" s="15" t="s">
         <v>8</v>
       </c>
@@ -2759,7 +2759,7 @@
       <c r="I81" s="19"/>
       <c r="J81" s="20"/>
     </row>
-    <row r="82" spans="2:10" x14ac:dyDescent="0.45">
+    <row r="82" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B82" s="15" t="s">
         <v>8</v>
       </c>
@@ -2782,7 +2782,7 @@
       <c r="I82" s="19"/>
       <c r="J82" s="20"/>
     </row>
-    <row r="83" spans="2:10" x14ac:dyDescent="0.45">
+    <row r="83" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B83" s="15" t="s">
         <v>8</v>
       </c>
@@ -2805,7 +2805,7 @@
       <c r="I83" s="19"/>
       <c r="J83" s="20"/>
     </row>
-    <row r="84" spans="2:10" x14ac:dyDescent="0.45">
+    <row r="84" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B84" s="15" t="s">
         <v>8</v>
       </c>
@@ -2828,7 +2828,7 @@
       <c r="I84" s="19"/>
       <c r="J84" s="20"/>
     </row>
-    <row r="85" spans="2:10" x14ac:dyDescent="0.45">
+    <row r="85" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B85" s="15" t="s">
         <v>8</v>
       </c>
@@ -2851,7 +2851,7 @@
       <c r="I85" s="19"/>
       <c r="J85" s="20"/>
     </row>
-    <row r="86" spans="2:10" x14ac:dyDescent="0.45">
+    <row r="86" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B86" s="15" t="s">
         <v>8</v>
       </c>
@@ -2874,7 +2874,7 @@
       <c r="I86" s="19"/>
       <c r="J86" s="20"/>
     </row>
-    <row r="87" spans="2:10" x14ac:dyDescent="0.45">
+    <row r="87" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B87" s="15" t="s">
         <v>8</v>
       </c>
@@ -2897,7 +2897,7 @@
       <c r="I87" s="19"/>
       <c r="J87" s="20"/>
     </row>
-    <row r="88" spans="2:10" x14ac:dyDescent="0.45">
+    <row r="88" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B88" s="15" t="s">
         <v>8</v>
       </c>
@@ -2920,7 +2920,7 @@
       <c r="I88" s="19"/>
       <c r="J88" s="20"/>
     </row>
-    <row r="89" spans="2:10" x14ac:dyDescent="0.45">
+    <row r="89" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B89" s="15" t="s">
         <v>8</v>
       </c>
@@ -2943,7 +2943,7 @@
       <c r="I89" s="19"/>
       <c r="J89" s="20"/>
     </row>
-    <row r="90" spans="2:10" x14ac:dyDescent="0.45">
+    <row r="90" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B90" s="15" t="s">
         <v>8</v>
       </c>
@@ -2966,7 +2966,7 @@
       <c r="I90" s="19"/>
       <c r="J90" s="20"/>
     </row>
-    <row r="91" spans="2:10" x14ac:dyDescent="0.45">
+    <row r="91" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B91" s="15" t="s">
         <v>8</v>
       </c>
@@ -2989,7 +2989,7 @@
       <c r="I91" s="19"/>
       <c r="J91" s="20"/>
     </row>
-    <row r="92" spans="2:10" x14ac:dyDescent="0.45">
+    <row r="92" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B92" s="15" t="s">
         <v>8</v>
       </c>
@@ -3012,7 +3012,7 @@
       <c r="I92" s="19"/>
       <c r="J92" s="20"/>
     </row>
-    <row r="93" spans="2:10" x14ac:dyDescent="0.45">
+    <row r="93" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B93" s="15" t="s">
         <v>8</v>
       </c>
@@ -3035,7 +3035,7 @@
       <c r="I93" s="19"/>
       <c r="J93" s="20"/>
     </row>
-    <row r="94" spans="2:10" x14ac:dyDescent="0.45">
+    <row r="94" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B94" s="15" t="s">
         <v>8</v>
       </c>
@@ -3058,7 +3058,7 @@
       <c r="I94" s="19"/>
       <c r="J94" s="20"/>
     </row>
-    <row r="95" spans="2:10" x14ac:dyDescent="0.45">
+    <row r="95" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B95" s="15" t="s">
         <v>8</v>
       </c>
@@ -3081,7 +3081,7 @@
       <c r="I95" s="19"/>
       <c r="J95" s="20"/>
     </row>
-    <row r="96" spans="2:10" x14ac:dyDescent="0.45">
+    <row r="96" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B96" s="15" t="s">
         <v>8</v>
       </c>
@@ -3104,7 +3104,7 @@
       <c r="I96" s="19"/>
       <c r="J96" s="20"/>
     </row>
-    <row r="97" spans="2:10" x14ac:dyDescent="0.45">
+    <row r="97" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B97" s="15" t="s">
         <v>8</v>
       </c>
@@ -3127,7 +3127,7 @@
       <c r="I97" s="19"/>
       <c r="J97" s="20"/>
     </row>
-    <row r="98" spans="2:10" x14ac:dyDescent="0.45">
+    <row r="98" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B98" s="15" t="s">
         <v>8</v>
       </c>
@@ -3150,7 +3150,7 @@
       <c r="I98" s="19"/>
       <c r="J98" s="20"/>
     </row>
-    <row r="99" spans="2:10" x14ac:dyDescent="0.45">
+    <row r="99" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B99" s="15" t="s">
         <v>8</v>
       </c>
@@ -3173,7 +3173,7 @@
       <c r="I99" s="19"/>
       <c r="J99" s="20"/>
     </row>
-    <row r="100" spans="2:10" x14ac:dyDescent="0.45">
+    <row r="100" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B100" s="15" t="s">
         <v>8</v>
       </c>
@@ -3196,7 +3196,7 @@
       <c r="I100" s="19"/>
       <c r="J100" s="20"/>
     </row>
-    <row r="101" spans="2:10" x14ac:dyDescent="0.45">
+    <row r="101" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B101" s="15" t="s">
         <v>8</v>
       </c>
@@ -3219,7 +3219,7 @@
       <c r="I101" s="19"/>
       <c r="J101" s="20"/>
     </row>
-    <row r="102" spans="2:10" x14ac:dyDescent="0.45">
+    <row r="102" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B102" s="15" t="s">
         <v>8</v>
       </c>
@@ -3242,7 +3242,7 @@
       <c r="I102" s="19"/>
       <c r="J102" s="20"/>
     </row>
-    <row r="103" spans="2:10" x14ac:dyDescent="0.45">
+    <row r="103" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B103" s="15" t="s">
         <v>8</v>
       </c>
@@ -3265,7 +3265,7 @@
       <c r="I103" s="19"/>
       <c r="J103" s="20"/>
     </row>
-    <row r="104" spans="2:10" x14ac:dyDescent="0.45">
+    <row r="104" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B104" s="15" t="s">
         <v>8</v>
       </c>
@@ -3288,7 +3288,7 @@
       <c r="I104" s="19"/>
       <c r="J104" s="20"/>
     </row>
-    <row r="105" spans="2:10" x14ac:dyDescent="0.45">
+    <row r="105" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B105" s="15" t="s">
         <v>8</v>
       </c>
@@ -3311,7 +3311,7 @@
       <c r="I105" s="19"/>
       <c r="J105" s="20"/>
     </row>
-    <row r="106" spans="2:10" x14ac:dyDescent="0.45">
+    <row r="106" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B106" s="15" t="s">
         <v>8</v>
       </c>
@@ -3334,7 +3334,7 @@
       <c r="I106" s="19"/>
       <c r="J106" s="20"/>
     </row>
-    <row r="107" spans="2:10" x14ac:dyDescent="0.45">
+    <row r="107" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B107" s="15" t="s">
         <v>8</v>
       </c>
@@ -3357,7 +3357,7 @@
       <c r="I107" s="19"/>
       <c r="J107" s="20"/>
     </row>
-    <row r="108" spans="2:10" x14ac:dyDescent="0.45">
+    <row r="108" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B108" s="15" t="s">
         <v>8</v>
       </c>
@@ -3380,7 +3380,7 @@
       <c r="I108" s="19"/>
       <c r="J108" s="20"/>
     </row>
-    <row r="109" spans="2:10" x14ac:dyDescent="0.45">
+    <row r="109" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B109" s="15" t="s">
         <v>8</v>
       </c>
@@ -3403,7 +3403,7 @@
       <c r="I109" s="19"/>
       <c r="J109" s="20"/>
     </row>
-    <row r="110" spans="2:10" x14ac:dyDescent="0.45">
+    <row r="110" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B110" s="15" t="s">
         <v>8</v>
       </c>
@@ -3426,7 +3426,7 @@
       <c r="I110" s="19"/>
       <c r="J110" s="20"/>
     </row>
-    <row r="111" spans="2:10" x14ac:dyDescent="0.45">
+    <row r="111" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B111" s="15" t="s">
         <v>8</v>
       </c>
@@ -3449,7 +3449,7 @@
       <c r="I111" s="19"/>
       <c r="J111" s="20"/>
     </row>
-    <row r="112" spans="2:10" x14ac:dyDescent="0.45">
+    <row r="112" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B112" s="15" t="s">
         <v>8</v>
       </c>
@@ -3472,7 +3472,7 @@
       <c r="I112" s="19"/>
       <c r="J112" s="20"/>
     </row>
-    <row r="113" spans="2:10" x14ac:dyDescent="0.45">
+    <row r="113" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B113" s="15" t="s">
         <v>8</v>
       </c>
@@ -3495,7 +3495,7 @@
       <c r="I113" s="19"/>
       <c r="J113" s="20"/>
     </row>
-    <row r="114" spans="2:10" x14ac:dyDescent="0.45">
+    <row r="114" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B114" s="15" t="s">
         <v>8</v>
       </c>
@@ -3518,7 +3518,7 @@
       <c r="I114" s="19"/>
       <c r="J114" s="20"/>
     </row>
-    <row r="115" spans="2:10" x14ac:dyDescent="0.45">
+    <row r="115" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B115" s="15" t="s">
         <v>8</v>
       </c>
@@ -3541,7 +3541,7 @@
       <c r="I115" s="19"/>
       <c r="J115" s="20"/>
     </row>
-    <row r="116" spans="2:10" x14ac:dyDescent="0.45">
+    <row r="116" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B116" s="15" t="s">
         <v>8</v>
       </c>
@@ -3564,7 +3564,7 @@
       <c r="I116" s="19"/>
       <c r="J116" s="20"/>
     </row>
-    <row r="117" spans="2:10" x14ac:dyDescent="0.45">
+    <row r="117" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B117" s="21" t="s">
         <v>8</v>
       </c>
@@ -3587,7 +3587,7 @@
       <c r="I117" s="25"/>
       <c r="J117" s="26"/>
     </row>
-    <row r="122" spans="2:10" x14ac:dyDescent="0.45">
+    <row r="122" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B122" s="32" t="s">
         <v>102</v>
       </c>
@@ -3598,7 +3598,7 @@
       <c r="I122" s="1"/>
       <c r="J122" s="1"/>
     </row>
-    <row r="123" spans="2:10" x14ac:dyDescent="0.45">
+    <row r="123" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B123" s="32" t="s">
         <v>101</v>
       </c>
